--- a/Data_clean/MCAS/Estados_US/Edos_USA_2016/WYOMING_2016.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2016/WYOMING_2016.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D348"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C4">
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C5">
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tepezalá</t>
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -573,7 +618,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C15">
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Reforma</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -667,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Bachíniva</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Balleza</t>
@@ -706,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Bocoyna</t>
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Buenaventura</t>
@@ -732,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -745,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Coronado</t>
@@ -758,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -771,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -784,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Dr. Belisario Domínguez</t>
@@ -797,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>El Tule</t>
@@ -810,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Galeana</t>
@@ -823,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -836,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Guachochi</t>
@@ -849,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Guadalupe y Calvo</t>
+          <t>Guadalupe Y Calvo</t>
         </is>
       </c>
       <c r="C36">
@@ -862,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Guerrero</t>
@@ -875,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C38">
@@ -888,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -901,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Janos</t>
@@ -914,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -927,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Julimes</t>
@@ -940,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -953,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Matachí</t>
@@ -966,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Meoqui</t>
@@ -979,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -992,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -1005,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1018,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Ojinaga</t>
@@ -1031,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -1044,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Temósachic</t>
@@ -1057,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1088,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Sabinas</t>
@@ -1101,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Saltillo</t>
@@ -1114,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1127,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Viesca</t>
@@ -1140,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1197,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1212,7 +1477,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1228,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1241,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1267,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1280,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1293,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1306,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1319,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1332,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1345,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1358,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1389,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Cuencamé</t>
@@ -1402,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1415,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1428,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>General Simón Bolívar</t>
@@ -1441,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1454,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1467,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -1480,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -1493,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Nazas</t>
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1519,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -1532,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>San Bernardo</t>
@@ -1545,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C88">
@@ -1558,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>San Luis del Cordero</t>
+          <t>San Luis Del Cordero</t>
         </is>
       </c>
       <c r="C89">
@@ -1571,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Santiago Papasquiaro</t>
@@ -1584,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Tamazula</t>
@@ -1597,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1610,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1625,12 +2035,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C94">
@@ -1641,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C95">
@@ -1654,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -1667,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1680,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1693,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -1706,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Cuautitlán Izcalli</t>
@@ -1719,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C101">
@@ -1732,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -1745,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -1758,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1771,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C105">
@@ -1784,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1797,9 +2267,14 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C107">
@@ -1810,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -1823,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -1836,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Tianguistenco</t>
@@ -1849,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C111">
@@ -1862,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1875,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -1888,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1919,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1932,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -1945,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -1958,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1971,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>León</t>
@@ -1984,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1997,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -2010,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Purísima del Rincón</t>
+          <t>Purísima Del Rincón</t>
         </is>
       </c>
       <c r="C123">
@@ -2023,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -2036,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -2049,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C126">
@@ -2062,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -2075,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2095,7 +2670,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C129">
@@ -2106,9 +2681,14 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C130">
@@ -2119,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C131">
@@ -2132,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -2145,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C133">
@@ -2158,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -2171,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C135">
@@ -2184,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -2197,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -2210,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -2223,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -2236,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -2249,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C141">
@@ -2262,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -2275,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C143">
@@ -2288,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -2301,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2332,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C147">
@@ -2345,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -2358,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Mineral del Chico</t>
+          <t>Mineral Del Chico</t>
         </is>
       </c>
       <c r="C149">
@@ -2371,9 +3041,14 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C150">
@@ -2384,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Pacula</t>
@@ -2397,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -2410,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -2423,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2454,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Ameca</t>
@@ -2467,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Arandas</t>
@@ -2480,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Atengo</t>
@@ -2493,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C159">
@@ -2506,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -2519,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Chimaltitán</t>
@@ -2532,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Cuautitlán de García Barragán</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C162">
@@ -2545,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -2558,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>El Salto</t>
@@ -2571,9 +3311,14 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C165">
@@ -2584,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2597,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Huejúcar</t>
@@ -2610,9 +3365,14 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C168">
@@ -2623,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -2636,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -2649,9 +3419,14 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C171">
@@ -2662,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -2675,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C173">
@@ -2688,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Sayula</t>
@@ -2701,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Talpa de Allende</t>
+          <t>Talpa De Allende</t>
         </is>
       </c>
       <c r="C175">
@@ -2714,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Tenamaxtlán</t>
@@ -2727,9 +3527,14 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C177">
@@ -2740,9 +3545,14 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C178">
@@ -2753,9 +3563,14 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C179">
@@ -2766,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -2779,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Tonaya</t>
@@ -2792,9 +3617,14 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C182">
@@ -2805,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Villa Corona</t>
@@ -2818,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -2831,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2844,9 +3689,14 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C186">
@@ -2857,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2888,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -2901,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Arteaga</t>
@@ -2914,9 +3779,14 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Coalcomán de Vázquez Pallares</t>
+          <t>Coalcomán De Vázquez Pallares</t>
         </is>
       </c>
       <c r="C191">
@@ -2927,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -2940,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -2953,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Cotija</t>
@@ -2966,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -2979,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Ixtlán</t>
@@ -2992,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -3005,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -3018,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -3031,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -3044,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Peribán</t>
@@ -3057,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -3070,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Queréndaro</t>
@@ -3083,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -3096,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -3109,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Tancítaro</t>
@@ -3122,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Tanhuato</t>
@@ -3135,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -3148,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -3161,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -3174,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -3187,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -3200,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -3213,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -3226,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -3239,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3270,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -3283,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Mazatepec</t>
@@ -3296,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Miacatlán</t>
@@ -3309,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -3322,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3342,7 +4362,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Amatlán de Cañas</t>
+          <t>Amatlán De Cañas</t>
         </is>
       </c>
       <c r="C223">
@@ -3353,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -3366,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Huajicori</t>
@@ -3379,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Ruíz</t>
@@ -3392,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -3405,9 +4445,14 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C228">
@@ -3418,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -3431,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -3444,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3475,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3495,7 +4560,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C234">
@@ -3506,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C235">
@@ -3519,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -3532,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>San Juan Lachao</t>
@@ -3545,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>San Mateo Piñas</t>
@@ -3558,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>San Miguel Panixtlahuaca</t>
@@ -3571,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>San Pedro Yólox</t>
@@ -3584,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -3597,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Santa María Tlahuitoltepec</t>
@@ -3610,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Santiago Amoltepec</t>
@@ -3623,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -3636,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Santiago Lachiguiri</t>
@@ -3649,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -3662,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -3675,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Villa Díaz Ordaz</t>
@@ -3688,9 +4823,14 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C249">
@@ -3701,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3732,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Cuautempan</t>
@@ -3745,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Esperanza</t>
@@ -3758,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Francisco Z. Mena</t>
@@ -3771,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Honey</t>
@@ -3784,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -3797,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Pahuatlán</t>
@@ -3810,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -3823,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -3836,9 +5021,14 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C260">
@@ -3849,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -3862,9 +5057,14 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C262">
@@ -3875,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Tlapacoya</t>
@@ -3888,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Xiutetelco</t>
@@ -3901,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -3914,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Zacapala</t>
@@ -3927,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3958,9 +5183,14 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C269">
@@ -3971,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4002,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -4015,9 +5255,14 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C273">
@@ -4028,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -4041,9 +5291,14 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C275">
@@ -4054,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -4067,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4098,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Badiraguato</t>
@@ -4111,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Cosalá</t>
@@ -4124,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -4137,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -4150,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -4163,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Sinaloa</t>
@@ -4176,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4207,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Bavispe</t>
@@ -4220,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -4233,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -4246,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -4259,9 +5579,14 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Nacozari de García</t>
+          <t>Nacozari De García</t>
         </is>
       </c>
       <c r="C291">
@@ -4272,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Navojoa</t>
@@ -4285,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Sahuaripa</t>
@@ -4298,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>San Luis Río Colorado</t>
@@ -4311,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4342,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4373,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -4386,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4417,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Atlangatepec</t>
@@ -4430,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -4443,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -4456,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Cuaxomulco</t>
@@ -4469,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>El Carmen Tequexquitla</t>
@@ -4482,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -4495,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Españita</t>
@@ -4508,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -4517,13 +5917,18 @@
         <v>88</v>
       </c>
       <c r="D309">
-        <v>0.09988649262202043</v>
+        <v>0.09988649262202044</v>
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Muñoz de Domingo Arenas</t>
+          <t>Muñoz De Domingo Arenas</t>
         </is>
       </c>
       <c r="C310">
@@ -4534,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -4547,9 +5957,14 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Tepetitla de Lardizábal</t>
+          <t>Tepetitla De Lardizábal</t>
         </is>
       </c>
       <c r="C312">
@@ -4560,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -4573,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -4586,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -4599,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4630,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Alvarado</t>
@@ -4643,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Calcahualco</t>
@@ -4656,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -4669,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Gutiérrez Zamora</t>
@@ -4682,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Jáltipan</t>
@@ -4695,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Naolinco</t>
@@ -4708,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -4721,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Soteapan</t>
@@ -4734,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Tempoal</t>
@@ -4747,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Tenochtitlán</t>
@@ -4760,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -4773,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -4786,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4817,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -4830,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -4843,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Genaro Codina</t>
@@ -4856,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -4869,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -4882,9 +6407,14 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C337">
@@ -4895,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -4908,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -4921,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -4934,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -4947,9 +6497,14 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C342">
@@ -4960,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -4973,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>Vetagrande</t>
@@ -4986,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -4999,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -5012,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5035,76 +6615,6 @@
       </c>
       <c r="D348">
         <v>1</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 814,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Marzo de 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
